--- a/frontend/e2e/fixtures/entries-with-errors.xlsx
+++ b/frontend/e2e/fixtures/entries-with-errors.xlsx
@@ -1,136 +1,127 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:workbookPr codeName="ThisWorkbook"/>
-  <x:bookViews>
-    <x:workbookView firstSheet="0" activeTab="0"/>
-  </x:bookViews>
-  <x:sheets>
-    <x:sheet name="Entries" sheetId="1" r:id="rId2"/>
-  </x:sheets>
-  <x:definedNames/>
-  <x:calcPr calcId="125725"/>
-</x:workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t>ParticipantName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ParticipantEmail</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BeerName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Style</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Collaborators</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ana Gómez</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ana@brew.example</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hop Cannon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>luis@brew.example</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Luis Pérez</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dark Matter</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Imperial Stout</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sam Roe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sam@brew.example</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Fizzy Lifting</x:t>
-  </x:si>
-  <x:si>
-    <x:t>99Z</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Casey Void</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Skunk Ale</x:t>
-  </x:si>
-</x:sst>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Entries" sheetId="1" state="visible" r:id="rId1"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
-    <x:numFmt numFmtId="0" formatCode=""/>
-  </x:numFmts>
-  <x:fonts count="1">
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="11"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-  </x:fonts>
-  <x:fills count="2">
-    <x:fill>
-      <x:patternFill patternType="none"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="gray125"/>
-    </x:fill>
-  </x:fills>
-  <x:borders count="1">
-    <x:border diagonalUp="0" diagonalDown="0">
-      <x:left style="none">
-        <x:color rgb="FF000000"/>
-      </x:left>
-      <x:right style="none">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="none">
-        <x:color rgb="FF000000"/>
-      </x:top>
-      <x:bottom style="none">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-      <x:diagonal style="none">
-        <x:color rgb="FF000000"/>
-      </x:diagonal>
-    </x:border>
-  </x:borders>
-  <x:cellStyleXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-  </x:cellStyleXfs>
-  <x:cellXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-  </x:cellXfs>
-  <x:cellStyles count="1">
-    <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </x:cellStyles>
-</x:styleSheet>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -417,91 +408,402 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:E5"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData>
-    <x:row r="1" spans="1:5">
-      <x:c r="A1" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B1" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C1" s="0" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D1" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E1" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:5">
-      <x:c r="A2" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B2" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:5">
-      <x:c r="A3" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:5">
-      <x:c r="A4" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:5">
-      <x:c r="A5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Marca temporal</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Dirección de correo electrónico</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Numero socio ACCE</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Nombre y apellidos</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Fecha de nacimiento</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Teléfono</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Categoria</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Estilo</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Grado alcohol: (%)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Número de botellas enviadas</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Fecha de elaboración</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Fecha de embotellado</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Maltas utilizadas</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lupulos utilizados</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Levadura utilizada</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Otros ingredientes</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Instrucciones de entrada</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:00:00</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ana@brew.example</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Ana Gómez</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1990-01-05</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>600100200</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Estilos clásicos</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>21A</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Pale</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Citra</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>US-05</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:05:00</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>luis@brew.example</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Luis Pérez</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1988-03-11</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>600100201</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Estilos clásicos</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Imperial Stout</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Roasted</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Magnum</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>S-04</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Servir a 12°C</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:10:00</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sam@brew.example</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Sam Roe</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1992-09-30</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>600100202</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Estilos clásicos</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>99Z</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Pilsner</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Saaz</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>W-34/70</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:15:00</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Casey Void</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1995-12-12</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>600100203</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Estilos clásicos</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>20C</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Hallertau</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>W-34/70</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>